--- a/_s4/S4_change_log.xlsx
+++ b/_s4/S4_change_log.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Items" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Change Log'!$A$4:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Change Log'!$A$4:$L$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan Tracker'!$A$4:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deck vs Site'!$A$4:$G$23</definedName>
   </definedNames>
@@ -654,13 +654,11 @@
           <t>Changes made</t>
         </is>
       </c>
-      <c r="B7" s="5">
-        <f>25-4</f>
-        <v/>
-      </c>
-      <c r="C7" s="6">
-        <f>25-4</f>
-        <v/>
+      <c r="B7" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>24</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -673,7 +671,7 @@
         </is>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIF('Change Log'!$K$5:$K$25,"Cleared*")</f>
+        <f>COUNTIF('Change Log'!$K$5:$K$28,"Cleared*")</f>
         <v/>
       </c>
     </row>
@@ -749,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2102,8 +2100,188 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>(uncommitted)</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>about.html</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Kevin Flick added as Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>(no CFO card for him; Gokul Madhavan listed as CFO)</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Kevin Flick, Chief Financial Officer. Bio: finance operator across energy and industrials, 20+ years. CFO and operating partner at Infinity Financial Group. A decade as EVP Finance at Canacol Energy, and transaction advisory at EY.</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>New CFO appointed Sep 2026. Bio drafted from his own LinkedIn profile, read 23 Sep 2026, and must be confirmed against his CV or appointment letter and matched to the S-4 word for word</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>User instruction</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>CEO + counsel</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>(uncommitted)</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>about.html</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Gokul Madhavan retitled</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Chief Strategy Officer</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Role change following the CFO appointment. The Aug 2026 deck still shows him as CFO and needs the same fix</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>User instruction</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>(uncommitted)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>about.html, style.css</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Leadership row widened to five</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>4-column grid, 5th card orphaned on its own row</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>5-column row on desktop, 3-up mid, 1-up on mobile</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Layout consequence of the new CFO card</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L25"/>
+  <autoFilter ref="A4:L28"/>
   <conditionalFormatting sqref="K5:K25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($K5,7)="Cleared"</formula>
@@ -2112,12 +2290,15 @@
       <formula>$K5="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="K5:K25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pending,Cleared,Cleared with edits,Reverted"</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No,Yes"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K26:K28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pending,Cleared,Cleared with edits,Reverted"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3614,12 +3795,12 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>One CFO</t>
+          <t>One CFO (deck is now out of date: Kevin Flick is CFO)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>India role retitled Finance Head</t>
+          <t>India role retitled Finance Head; Kevin Flick added as CFO; Gokul moved to Chief Strategy Officer. The deck still needs the same change</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">

--- a/_s4/S4_change_log.xlsx
+++ b/_s4/S4_change_log.xlsx
@@ -2131,7 +2131,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Kevin Flick, Chief Financial Officer. Bio: finance operator across energy and industrials, 20+ years. CFO and operating partner at Infinity Financial Group. A decade as EVP Finance at Canacol Energy, and transaction advisory at EY.</t>
+          <t>Kevin Flick, Chief Financial Officer. Bio: Two decades in the finance seat of energy and industrial businesses. Transaction advisory at EY, ten years as EVP Finance at Canacol Energy, then CFO and operating partner at Infinity Financial Group. Joined NEMI in September 2026.</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">

--- a/_s4/S4_change_log.xlsx
+++ b/_s4/S4_change_log.xlsx
@@ -2131,12 +2131,12 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Kevin Flick, Chief Financial Officer. Bio: Two decades in the finance seat of energy and industrial businesses. Transaction advisory at EY, ten years as EVP Finance at Canacol Energy, then CFO and operating partner at Infinity Financial Group. Joined NEMI in September 2026.</t>
+          <t>Kevin Flick, Chief Financial Officer. Bio: Two decades in senior finance roles across energy and industrial businesses. Transactions, reporting and finance operations, built for companies going through change.</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>New CFO appointed Sep 2026. Bio drafted from his own LinkedIn profile, read 23 Sep 2026, and must be confirmed against his CV or appointment letter and matched to the S-4 word for word</t>
+          <t>New CFO appointed Sep 2026. Bio kept general on purpose: no employer names or dates on the site until his CV or appointment letter is confirmed and the S-4 bio is set</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">

--- a/_s4/S4_change_log.xlsx
+++ b/_s4/S4_change_log.xlsx
@@ -2131,12 +2131,12 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Kevin Flick, Chief Financial Officer. Bio: Two decades in senior finance roles across energy and industrial businesses. Transactions, reporting and finance operations, built for companies going through change.</t>
+          <t>Kevin Flick, Chief Financial Officer. Bio: Two decades in senior finance roles across energy and industrial businesses, including a decade at Canacol Energy and transaction advisory at EY.</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>New CFO appointed Sep 2026. Bio kept general on purpose: no employer names or dates on the site until his CV or appointment letter is confirmed and the S-4 bio is set</t>
+          <t>New CFO appointed Sep 2026. Two employers named, taken from his own LinkedIn profile, read 23 Sep 2026. Confirm both against his CV or appointment letter before this goes live, and match the S-4 bio</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">

--- a/_s4/S4_change_log.xlsx
+++ b/_s4/S4_change_log.xlsx
@@ -2136,7 +2136,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>New CFO appointed Sep 2026. Two employers named, taken from his own LinkedIn profile, read 23 Sep 2026. Confirm both against his CV or appointment letter before this goes live, and match the S-4 bio</t>
+          <t>New CFO appointed Sep 2026. Two employers named, taken from his own LinkedIn profile, read 23 Sep 2026. Confirm both against his CV or appointment letter before this goes live, and match the S-4 bio. Copy approved internally 23 Sep 2026. Still to do before it goes live: confirm Canacol Energy and EY against his CV or appointment letter, get his written sign-off, and match the S-4 bio</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">

--- a/_s4/S4_change_log.xlsx
+++ b/_s4/S4_change_log.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Items" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Change Log'!$A$4:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Change Log'!$A$4:$L$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan Tracker'!$A$4:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deck vs Site'!$A$4:$G$23</definedName>
   </definedNames>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIF('Change Log'!$K$5:$K$28,"Cleared*")</f>
+        <f>COUNTIF('Change Log'!$K$5:$K$29,"Cleared*")</f>
         <v/>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2280,8 +2280,68 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>(uncommitted)</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>about.html</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Gokul Madhavan bio reframed for the strategy title</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Supported M&amp;A integrations, built digital finance operations, led digital transformations.</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Corporate development and transformation. M&amp;A integration, digital finance operations, and the work of turning strategy into operating plans across the group.</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>His title changed to Chief Strategy Officer but the bio still described finance work. Reframed using only what the old bio already claimed; nothing new asserted. Replace with his own wording and match the S-4 bio</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>User instruction</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L28"/>
+  <autoFilter ref="A4:L29"/>
   <conditionalFormatting sqref="K5:K25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($K5,7)="Cleared"</formula>
